--- a/output/pdf_financials_xlsx/SI.xlsx
+++ b/output/pdf_financials_xlsx/SI.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.16384</v>
+        <v>-0.16384</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9417450000000001</v>
+        <v>-0.9417450000000001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.165704</v>
+        <v>-1.165704</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.16384</v>
+        <v>-0.16384</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.9417450000000001</v>
+        <v>-0.9417450000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.165704</v>
+        <v>-1.165704</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.16384</v>
+        <v>-0.16384</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.9417450000000001</v>
+        <v>-0.9417450000000001</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.165704</v>
+        <v>-1.165704</v>
       </c>
     </row>
     <row r="24">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-5.461333</v>
+        <v>5.461333</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.545257</v>
+        <v>2.545257</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-6.476133</v>
+        <v>6.476133</v>
       </c>
     </row>
     <row r="27">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.16384</v>
+        <v>-0.16384</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.9417450000000001</v>
+        <v>-0.9417450000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.165704</v>
+        <v>-1.165704</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.16384</v>
+        <v>-0.16384</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.9417450000000001</v>
+        <v>-0.9417450000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.165704</v>
+        <v>-1.165704</v>
       </c>
     </row>
     <row r="30">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.134132</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.151721</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.42965</v>
       </c>
     </row>
     <row r="93">
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>0.004418</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.146962</v>
+        <v>-0.143081</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.592651</v>
       </c>
     </row>
     <row r="119">
@@ -3102,7 +3102,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3414,7 +3418,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.134132</v>
       </c>
@@ -3722,7 +3730,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.004418</v>
       </c>
@@ -4794,13 +4806,13 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.16384</v>
+        <v>-0.16384</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.9417450000000001</v>
+        <v>-0.9417450000000001</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1.165704</v>
+        <v>-1.165704</v>
       </c>
     </row>
     <row r="70">

--- a/output/pdf_financials_xlsx/SI.xlsx
+++ b/output/pdf_financials_xlsx/SI.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000808</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000145</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000337</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.16384</v>
+        <v>-0.163032</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.9417450000000001</v>
+        <v>-0.9416</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.165704</v>
+        <v>-1.165367</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.16384</v>
+        <v>-0.163032</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.9417450000000001</v>
+        <v>-0.9416</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.165704</v>
+        <v>-1.165367</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.536483</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.383399</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.174235</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.536483</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.383399</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.174235</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.536483</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.428399</v>
+        <v>0.045</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.285685</v>
+        <v>0.11145</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
